--- a/input/attachments/ig-assets/IPS_FHIR_to_CDISC_SDTM/09_StructureDefinition-DiagnosticReport-uv-ips_to_SDTM.xlsx
+++ b/input/attachments/ig-assets/IPS_FHIR_to_CDISC_SDTM/09_StructureDefinition-DiagnosticReport-uv-ips_to_SDTM.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28609"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29406"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cdisc-my.sharepoint.com/personal/rbaker_cdisc_org/Documents/1 Real World Data - RWD/1_XSHARE/Spreadsheets for project/IPS FHIR 1.1.0 to SDTMIG 3.4_2024-Nov/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="210" documentId="8_{BDA11FFF-4F91-4964-BF23-D700DFBEB416}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{65D5BFB4-7910-4990-B137-3D2830501DDD}"/>
+  <xr:revisionPtr revIDLastSave="211" documentId="8_{BDA11FFF-4F91-4964-BF23-D700DFBEB416}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{905A4926-ECEE-45CC-A108-32737C92D52A}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="3" activeTab="3" xr2:uid="{2461E1A9-8523-4D25-B35A-8F843D676FD1}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="3" activeTab="6" xr2:uid="{2461E1A9-8523-4D25-B35A-8F843D676FD1}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="7" r:id="rId1"/>
@@ -1737,8 +1737,7 @@
     <t xml:space="preserve">CDISC SDTM Study Identifier/STUDYID </t>
   </si>
   <si>
-    <t xml:space="preserve">For each clinical research study, populate the STUDYID variable with a default value "RWDTOSDTM-YYYYMMDD" where the date is the date on which the FHIR dataset was converted to create SDTM datasets.
-</t>
+    <t>In case there is no FHIR study ID (ResearchStudy or ResearchDefinition) available for the patient for which the immunization data is mapped, populate the STUDYID variable with a default value "RWDTOSDTM-YYYYMMDD" where the date is the date on which the FHIR dataset was converted to create SDTM datasets.</t>
   </si>
   <si>
     <t xml:space="preserve">Study Identifier/STUDYID is a variable in CDISC Demographics domain that is a unique identifier for a study. STUDYID is used as a key in all CDISC SDTM datasets.
@@ -2258,7 +2257,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="16">
+  <fonts count="17">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -2364,6 +2363,13 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="12">
@@ -2553,7 +2559,7 @@
     <xf numFmtId="0" fontId="11" fillId="2" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="75">
+  <cellXfs count="76">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -2710,44 +2716,47 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="5" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -10944,7 +10953,7 @@
         <v>398</v>
       </c>
       <c r="AP14" s="44"/>
-      <c r="AQ14" s="63" t="s">
+      <c r="AQ14" s="62" t="s">
         <v>399</v>
       </c>
     </row>
@@ -11061,13 +11070,13 @@
       <c r="AN15" s="43" t="s">
         <v>397</v>
       </c>
-      <c r="AO15" s="64" t="s">
+      <c r="AO15" s="63" t="s">
         <v>400</v>
       </c>
       <c r="AP15" s="44" t="s">
         <v>401</v>
       </c>
-      <c r="AQ15" s="65" t="s">
+      <c r="AQ15" s="64" t="s">
         <v>402</v>
       </c>
     </row>
@@ -14359,442 +14368,442 @@
       </c>
     </row>
     <row r="2" spans="1:8" ht="100.9">
-      <c r="A2" s="66">
+      <c r="A2" s="65">
         <v>1</v>
       </c>
-      <c r="B2" s="66">
+      <c r="B2" s="65">
         <v>1</v>
       </c>
-      <c r="C2" s="64" t="s">
+      <c r="C2" s="63" t="s">
         <v>428</v>
       </c>
-      <c r="D2" s="66" t="s">
+      <c r="D2" s="65" t="s">
         <v>429</v>
       </c>
-      <c r="E2" s="66" t="s">
+      <c r="E2" s="65" t="s">
         <v>430</v>
       </c>
-      <c r="F2" s="67" t="s">
+      <c r="F2" s="66" t="s">
         <v>414</v>
       </c>
-      <c r="G2" s="67" t="s">
+      <c r="G2" s="66" t="s">
         <v>414</v>
       </c>
-      <c r="H2" s="68"/>
+      <c r="H2" s="67"/>
     </row>
     <row r="3" spans="1:8" ht="144">
-      <c r="A3" s="66">
+      <c r="A3" s="65">
         <v>2</v>
       </c>
-      <c r="B3" s="66">
+      <c r="B3" s="65">
         <v>2</v>
       </c>
-      <c r="C3" s="64" t="s">
+      <c r="C3" s="63" t="s">
         <v>428</v>
       </c>
-      <c r="D3" s="66" t="s">
+      <c r="D3" s="65" t="s">
         <v>431</v>
       </c>
-      <c r="E3" s="66" t="s">
+      <c r="E3" s="65" t="s">
         <v>432</v>
       </c>
-      <c r="F3" s="67" t="s">
+      <c r="F3" s="66" t="s">
         <v>433</v>
       </c>
-      <c r="G3" s="67" t="s">
+      <c r="G3" s="66" t="s">
         <v>434</v>
       </c>
-      <c r="H3" s="63" t="s">
+      <c r="H3" s="62" t="s">
         <v>399</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="409.6">
-      <c r="A4" s="66">
+      <c r="A4" s="65">
         <v>3</v>
       </c>
-      <c r="B4" s="66">
+      <c r="B4" s="65">
         <v>3</v>
       </c>
-      <c r="C4" s="64" t="s">
+      <c r="C4" s="63" t="s">
         <v>428</v>
       </c>
-      <c r="D4" s="66" t="s">
+      <c r="D4" s="65" t="s">
         <v>435</v>
       </c>
-      <c r="E4" s="65" t="s">
+      <c r="E4" s="64" t="s">
         <v>436</v>
       </c>
-      <c r="F4" s="64" t="s">
+      <c r="F4" s="63" t="s">
         <v>433</v>
       </c>
-      <c r="G4" s="64" t="s">
+      <c r="G4" s="63" t="s">
         <v>400</v>
       </c>
-      <c r="H4" s="65" t="s">
+      <c r="H4" s="64" t="s">
         <v>402</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="86.45">
-      <c r="A5" s="66">
+      <c r="A5" s="65">
         <v>4</v>
       </c>
-      <c r="B5" s="66">
+      <c r="B5" s="65">
         <v>3</v>
       </c>
-      <c r="C5" s="64" t="s">
+      <c r="C5" s="63" t="s">
         <v>428</v>
       </c>
-      <c r="D5" s="66" t="s">
+      <c r="D5" s="65" t="s">
         <v>437</v>
       </c>
-      <c r="E5" s="65" t="s">
+      <c r="E5" s="64" t="s">
         <v>436</v>
       </c>
-      <c r="F5" s="64" t="s">
+      <c r="F5" s="63" t="s">
         <v>433</v>
       </c>
-      <c r="G5" s="64" t="s">
+      <c r="G5" s="63" t="s">
         <v>438</v>
       </c>
-      <c r="H5" s="65" t="s">
+      <c r="H5" s="64" t="s">
         <v>439</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="409.6">
-      <c r="A6" s="66">
+      <c r="A6" s="65">
         <v>5</v>
       </c>
-      <c r="B6" s="66">
+      <c r="B6" s="65">
         <v>4</v>
       </c>
-      <c r="C6" s="64" t="s">
+      <c r="C6" s="63" t="s">
         <v>428</v>
       </c>
-      <c r="D6" s="69" t="s">
+      <c r="D6" s="68" t="s">
         <v>440</v>
       </c>
-      <c r="E6" s="65" t="s">
+      <c r="E6" s="64" t="s">
         <v>220</v>
       </c>
-      <c r="F6" s="64" t="s">
+      <c r="F6" s="63" t="s">
         <v>403</v>
       </c>
-      <c r="G6" s="64" t="s">
+      <c r="G6" s="63" t="s">
         <v>404</v>
       </c>
-      <c r="H6" s="69" t="s">
+      <c r="H6" s="68" t="s">
         <v>441</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="57.6">
-      <c r="A7" s="66">
+      <c r="A7" s="65">
         <v>6</v>
       </c>
-      <c r="B7" s="66">
+      <c r="B7" s="65">
         <v>5</v>
       </c>
-      <c r="C7" s="64" t="s">
+      <c r="C7" s="63" t="s">
         <v>428</v>
       </c>
-      <c r="D7" s="69" t="s">
+      <c r="D7" s="68" t="s">
         <v>442</v>
       </c>
-      <c r="E7" s="65" t="s">
+      <c r="E7" s="64" t="s">
         <v>443</v>
       </c>
-      <c r="F7" s="70" t="s">
+      <c r="F7" s="69" t="s">
         <v>406</v>
       </c>
-      <c r="G7" s="70" t="s">
+      <c r="G7" s="69" t="s">
         <v>407</v>
       </c>
-      <c r="H7" s="69" t="s">
+      <c r="H7" s="68" t="s">
         <v>444</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="115.15">
-      <c r="A8" s="66">
+      <c r="A8" s="65">
         <v>7</v>
       </c>
-      <c r="B8" s="66">
+      <c r="B8" s="65">
         <v>6</v>
       </c>
-      <c r="C8" s="64" t="s">
+      <c r="C8" s="63" t="s">
         <v>428</v>
       </c>
-      <c r="D8" s="69" t="s">
+      <c r="D8" s="68" t="s">
         <v>445</v>
       </c>
-      <c r="E8" s="71" t="s">
+      <c r="E8" s="70" t="s">
         <v>446</v>
       </c>
-      <c r="F8" s="72" t="s">
+      <c r="F8" s="71" t="s">
         <v>433</v>
       </c>
-      <c r="G8" s="72" t="s">
+      <c r="G8" s="71" t="s">
         <v>409</v>
       </c>
-      <c r="H8" s="72" t="s">
+      <c r="H8" s="71" t="s">
         <v>447</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="115.15">
-      <c r="A9" s="66">
+      <c r="A9" s="65">
         <v>8</v>
       </c>
-      <c r="B9" s="66">
+      <c r="B9" s="65">
         <v>7</v>
       </c>
-      <c r="C9" s="64" t="s">
+      <c r="C9" s="63" t="s">
         <v>428</v>
       </c>
-      <c r="D9" s="69" t="s">
+      <c r="D9" s="68" t="s">
         <v>448</v>
       </c>
-      <c r="E9" s="66" t="s">
+      <c r="E9" s="65" t="s">
         <v>449</v>
       </c>
-      <c r="F9" s="64" t="s">
+      <c r="F9" s="63" t="s">
         <v>433</v>
       </c>
-      <c r="G9" s="64" t="s">
+      <c r="G9" s="63" t="s">
         <v>450</v>
       </c>
-      <c r="H9" s="69" t="s">
+      <c r="H9" s="68" t="s">
         <v>451</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="158.44999999999999">
-      <c r="A10" s="66">
+      <c r="A10" s="65">
         <v>9</v>
       </c>
-      <c r="B10" s="66">
+      <c r="B10" s="65">
         <v>8</v>
       </c>
-      <c r="C10" s="64" t="s">
+      <c r="C10" s="63" t="s">
         <v>428</v>
       </c>
-      <c r="D10" s="65" t="s">
+      <c r="D10" s="64" t="s">
         <v>452</v>
       </c>
       <c r="E10" s="61" t="s">
         <v>453</v>
       </c>
-      <c r="F10" s="72" t="s">
+      <c r="F10" s="71" t="s">
         <v>433</v>
       </c>
-      <c r="G10" s="72" t="s">
+      <c r="G10" s="71" t="s">
         <v>419</v>
       </c>
-      <c r="H10" s="72" t="s">
+      <c r="H10" s="71" t="s">
         <v>454</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="409.6">
-      <c r="A11" s="66">
+      <c r="A11" s="65">
         <v>10</v>
       </c>
-      <c r="B11" s="64">
+      <c r="B11" s="63">
         <v>9</v>
       </c>
-      <c r="C11" s="64" t="s">
+      <c r="C11" s="63" t="s">
         <v>428</v>
       </c>
-      <c r="D11" s="69" t="s">
+      <c r="D11" s="68" t="s">
         <v>455</v>
       </c>
-      <c r="E11" s="65" t="s">
+      <c r="E11" s="64" t="s">
         <v>456</v>
       </c>
-      <c r="F11" s="70" t="s">
+      <c r="F11" s="69" t="s">
         <v>457</v>
       </c>
-      <c r="G11" s="70" t="s">
+      <c r="G11" s="69" t="s">
         <v>458</v>
       </c>
-      <c r="H11" s="69" t="s">
+      <c r="H11" s="68" t="s">
         <v>459</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="172.9">
-      <c r="A12" s="66">
+      <c r="A12" s="65">
         <v>11</v>
       </c>
-      <c r="B12" s="73">
+      <c r="B12" s="72">
         <v>9</v>
       </c>
-      <c r="C12" s="64" t="s">
+      <c r="C12" s="63" t="s">
         <v>428</v>
       </c>
-      <c r="D12" s="69" t="s">
+      <c r="D12" s="68" t="s">
         <v>460</v>
       </c>
-      <c r="E12" s="65" t="s">
+      <c r="E12" s="64" t="s">
         <v>461</v>
       </c>
-      <c r="F12" s="70" t="s">
+      <c r="F12" s="69" t="s">
         <v>433</v>
       </c>
-      <c r="G12" s="70" t="s">
+      <c r="G12" s="69" t="s">
         <v>462</v>
       </c>
-      <c r="H12" s="69" t="s">
+      <c r="H12" s="68" t="s">
         <v>463</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="316.89999999999998">
-      <c r="A13" s="66">
+      <c r="A13" s="65">
         <v>12</v>
       </c>
-      <c r="B13" s="73">
+      <c r="B13" s="72">
         <v>9</v>
       </c>
-      <c r="C13" s="64" t="s">
+      <c r="C13" s="63" t="s">
         <v>428</v>
       </c>
-      <c r="D13" s="66" t="s">
+      <c r="D13" s="65" t="s">
         <v>464</v>
       </c>
-      <c r="E13" s="66" t="s">
+      <c r="E13" s="65" t="s">
         <v>465</v>
       </c>
-      <c r="F13" s="64" t="s">
+      <c r="F13" s="63" t="s">
         <v>433</v>
       </c>
-      <c r="G13" s="64" t="s">
+      <c r="G13" s="63" t="s">
         <v>466</v>
       </c>
-      <c r="H13" s="65" t="s">
+      <c r="H13" s="64" t="s">
         <v>467</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="259.14999999999998">
-      <c r="A14" s="66">
+      <c r="A14" s="65">
         <v>13</v>
       </c>
-      <c r="B14" s="64">
+      <c r="B14" s="63">
         <v>10</v>
       </c>
-      <c r="C14" s="64" t="s">
+      <c r="C14" s="63" t="s">
         <v>428</v>
       </c>
-      <c r="D14" s="66" t="s">
+      <c r="D14" s="65" t="s">
         <v>468</v>
       </c>
-      <c r="E14" s="66" t="s">
+      <c r="E14" s="65" t="s">
         <v>469</v>
       </c>
-      <c r="F14" s="64" t="s">
+      <c r="F14" s="63" t="s">
         <v>433</v>
       </c>
-      <c r="G14" s="64" t="s">
+      <c r="G14" s="63" t="s">
         <v>470</v>
       </c>
-      <c r="H14" s="65" t="s">
+      <c r="H14" s="64" t="s">
         <v>471</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="100.9">
-      <c r="A15" s="66">
+      <c r="A15" s="65">
         <v>14</v>
       </c>
-      <c r="B15" s="64">
+      <c r="B15" s="63">
         <v>10</v>
       </c>
-      <c r="C15" s="64" t="s">
+      <c r="C15" s="63" t="s">
         <v>428</v>
       </c>
-      <c r="D15" s="66" t="s">
+      <c r="D15" s="65" t="s">
         <v>472</v>
       </c>
-      <c r="E15" s="71" t="s">
+      <c r="E15" s="70" t="s">
         <v>473</v>
       </c>
-      <c r="F15" s="64" t="s">
+      <c r="F15" s="63" t="s">
         <v>414</v>
       </c>
-      <c r="G15" s="64" t="s">
+      <c r="G15" s="63" t="s">
         <v>414</v>
       </c>
-      <c r="H15" s="63" t="s">
+      <c r="H15" s="62" t="s">
         <v>474</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="158.44999999999999">
-      <c r="A16" s="66">
+      <c r="A16" s="65">
         <v>15</v>
       </c>
-      <c r="B16" s="64">
+      <c r="B16" s="63">
         <v>10</v>
       </c>
-      <c r="C16" s="64" t="s">
+      <c r="C16" s="63" t="s">
         <v>428</v>
       </c>
-      <c r="D16" s="66" t="s">
+      <c r="D16" s="65" t="s">
         <v>475</v>
       </c>
-      <c r="E16" s="66" t="s">
+      <c r="E16" s="65" t="s">
         <v>476</v>
       </c>
-      <c r="F16" s="64" t="s">
+      <c r="F16" s="63" t="s">
         <v>414</v>
       </c>
-      <c r="G16" s="64" t="s">
+      <c r="G16" s="63" t="s">
         <v>414</v>
       </c>
-      <c r="H16" s="63" t="s">
+      <c r="H16" s="62" t="s">
         <v>474</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="100.9">
-      <c r="A17" s="66">
+      <c r="A17" s="65">
         <v>16</v>
       </c>
-      <c r="B17" s="64">
+      <c r="B17" s="63">
         <v>10</v>
       </c>
-      <c r="C17" s="64" t="s">
+      <c r="C17" s="63" t="s">
         <v>428</v>
       </c>
-      <c r="D17" s="74" t="s">
+      <c r="D17" s="73" t="s">
         <v>477</v>
       </c>
-      <c r="E17" s="66" t="s">
+      <c r="E17" s="65" t="s">
         <v>478</v>
       </c>
-      <c r="F17" s="64" t="s">
+      <c r="F17" s="63" t="s">
         <v>414</v>
       </c>
-      <c r="G17" s="64" t="s">
+      <c r="G17" s="63" t="s">
         <v>414</v>
       </c>
-      <c r="H17" s="63" t="s">
+      <c r="H17" s="62" t="s">
         <v>474</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="100.9">
-      <c r="A18" s="66">
+      <c r="A18" s="65">
         <v>17</v>
       </c>
-      <c r="B18" s="66">
+      <c r="B18" s="65">
         <v>10</v>
       </c>
-      <c r="C18" s="64" t="s">
+      <c r="C18" s="63" t="s">
         <v>428</v>
       </c>
-      <c r="D18" s="66" t="s">
+      <c r="D18" s="65" t="s">
         <v>479</v>
       </c>
-      <c r="E18" s="66" t="s">
+      <c r="E18" s="65" t="s">
         <v>480</v>
       </c>
-      <c r="F18" s="64" t="s">
+      <c r="F18" s="63" t="s">
         <v>414</v>
       </c>
-      <c r="G18" s="64" t="s">
+      <c r="G18" s="63" t="s">
         <v>414</v>
       </c>
-      <c r="H18" s="63" t="s">
+      <c r="H18" s="62" t="s">
         <v>474</v>
       </c>
     </row>
@@ -14918,10 +14927,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
-      <c r="A1" s="62" t="s">
+      <c r="A1" s="74" t="s">
         <v>481</v>
       </c>
-      <c r="B1" s="62"/>
+      <c r="B1" s="74"/>
       <c r="C1" s="14"/>
       <c r="D1" s="14"/>
     </row>
@@ -14965,14 +14974,14 @@
         <v>489</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="57.6">
+    <row r="5" spans="1:4" ht="57.75">
       <c r="A5" s="8">
         <v>3</v>
       </c>
       <c r="B5" s="8" t="s">
         <v>490</v>
       </c>
-      <c r="C5" s="12" t="s">
+      <c r="C5" s="75" t="s">
         <v>491</v>
       </c>
       <c r="D5" s="6" t="s">
@@ -17319,17 +17328,19 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="526f0e77-c4a1-4bb9-a981-799c4b6cfc2b" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="a46baf18-fe18-4a25-9dd7-6596c31699af">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100699A48AB9E19DA4AB64847A071655FFB" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="9c43450b8c34e20acaf1756fc6612395">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="a46baf18-fe18-4a25-9dd7-6596c31699af" xmlns:ns3="526f0e77-c4a1-4bb9-a981-799c4b6cfc2b" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="0a2045bb9c165ab785731dcc392b30c8" ns2:_="" ns3:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100699A48AB9E19DA4AB64847A071655FFB" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="fb735b3d8e016bb6466dda22f76823b1">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="a46baf18-fe18-4a25-9dd7-6596c31699af" xmlns:ns3="526f0e77-c4a1-4bb9-a981-799c4b6cfc2b" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="47d37a05d05a9fe6c5dd27e72eaf287f" ns2:_="" ns3:_="">
     <xsd:import namespace="a46baf18-fe18-4a25-9dd7-6596c31699af"/>
     <xsd:import namespace="526f0e77-c4a1-4bb9-a981-799c4b6cfc2b"/>
     <xsd:element name="properties">
@@ -17352,6 +17363,7 @@
                 <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
                 <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
                 <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceBillingMetadata" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
           </xsd:element>
@@ -17419,6 +17431,11 @@
     <xsd:element name="MediaServiceLocation" ma:index="20" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceBillingMetadata" ma:index="23" nillable="true" ma:displayName="MediaServiceBillingMetadata" ma:hidden="true" ma:internalName="MediaServiceBillingMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
   </xsd:schema>
@@ -17563,24 +17580,22 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="526f0e77-c4a1-4bb9-a981-799c4b6cfc2b" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="a46baf18-fe18-4a25-9dd7-6596c31699af">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9DC5A1C1-00CD-454D-B1EA-D15E98A957DC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DFF2EFC8-0BC9-418F-9E03-CDCD2690AA66}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A731DB4F-4D1C-4F9A-A431-8CB3DEBAB7D8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9CEF5FDB-E926-4D32-8BFB-967461C2C945}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DFF2EFC8-0BC9-418F-9E03-CDCD2690AA66}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9DC5A1C1-00CD-454D-B1EA-D15E98A957DC}"/>
 </file>